--- a/plan/backlog-freshflow-mvp-12-tuan-updated.xlsx
+++ b/plan/backlog-freshflow-mvp-12-tuan-updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FreshFlow\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC5EAC5-4F1C-436E-B89E-0EB7889CFE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D788D1-CD21-4C80-8000-6A1BB8D19234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/plan/backlog-freshflow-mvp-12-tuan-updated.xlsx
+++ b/plan/backlog-freshflow-mvp-12-tuan-updated.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FreshFlow\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D788D1-CD21-4C80-8000-6A1BB8D19234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58DFAF0-6A9D-4254-981E-9AC792CA52C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="1617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="1618">
   <si>
     <t>Task ID</t>
   </si>
@@ -4897,6 +4897,9 @@
   </si>
   <si>
     <t xml:space="preserve">LÀM NHẦM --- CẦN XXEM LẠI XEM ĐÃ ĐỦ CHƯA </t>
+  </si>
+  <si>
+    <t>In Progress</t>
   </si>
 </sst>
 </file>
@@ -5731,7 +5734,7 @@
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="6" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -5784,7 +5787,7 @@
       </c>
       <c r="O6" s="3"/>
       <c r="P6" s="6" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -5837,7 +5840,7 @@
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>71</v>
+        <v>1617</v>
       </c>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
@@ -5890,7 +5893,7 @@
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
-        <v>71</v>
+        <v>1617</v>
       </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
@@ -15329,7 +15332,7 @@
       </c>
       <c r="B11" s="7" t="str">
         <f>COUNTIF('Backlog 12 Tuan'!P:P,"Done")&amp;" / "&amp;COUNTA('Backlog 12 Tuan'!A:A)-1&amp;" task Done"</f>
-        <v>2 / 168 task Done</v>
+        <v>4 / 168 task Done</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15338,7 +15341,7 @@
       </c>
       <c r="B12" s="8">
         <f>COUNTIF('Backlog 12 Tuan'!P:P,"Done")/(COUNTA('Backlog 12 Tuan'!A:A)-1)</f>
-        <v>1.1904761904761904E-2</v>
+        <v>2.3809523809523808E-2</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/plan/backlog-freshflow-mvp-12-tuan-updated.xlsx
+++ b/plan/backlog-freshflow-mvp-12-tuan-updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FreshFlow\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58DFAF0-6A9D-4254-981E-9AC792CA52C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99A07B0-0871-4FC3-93C8-3FD03B1269E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>1617</v>
+        <v>33</v>
       </c>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
-        <v>1617</v>
+        <v>33</v>
       </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3" t="s">
-        <v>71</v>
+        <v>1617</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="B11" s="7" t="str">
         <f>COUNTIF('Backlog 12 Tuan'!P:P,"Done")&amp;" / "&amp;COUNTA('Backlog 12 Tuan'!A:A)-1&amp;" task Done"</f>
-        <v>4 / 168 task Done</v>
+        <v>7 / 168 task Done</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="B12" s="8">
         <f>COUNTIF('Backlog 12 Tuan'!P:P,"Done")/(COUNTA('Backlog 12 Tuan'!A:A)-1)</f>
-        <v>2.3809523809523808E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
